--- a/data/internalStats2/File1/RPT_RPT7043243328387RJ_internalStats2.xlsx
+++ b/data/internalStats2/File1/RPT_RPT7043243328387RJ_internalStats2.xlsx
@@ -2168,19 +2168,19 @@
         </is>
       </c>
       <c r="P8" s="158" t="n">
-        <v>47492.99344515815</v>
+        <v>47492.99344515816</v>
       </c>
       <c r="Q8" s="159" t="n">
         <v>0</v>
       </c>
       <c r="R8" s="159" t="n">
-        <v>70.28327983516802</v>
+        <v>70.28327983516805</v>
       </c>
       <c r="S8" s="160" t="n">
         <v>154.5769415687428</v>
       </c>
       <c r="T8" s="161" t="n">
-        <v>47717.85366656206</v>
+        <v>47717.85366656208</v>
       </c>
     </row>
     <row r="9">
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="P9" s="162" t="n">
-        <v>59576.06924993483</v>
+        <v>59576.06924993484</v>
       </c>
       <c r="Q9" s="163" t="n">
         <v>0</v>
@@ -2199,7 +2199,7 @@
         <v>592.3635368868523</v>
       </c>
       <c r="S9" s="164" t="n">
-        <v>390.7507494116553</v>
+        <v>390.7507494116552</v>
       </c>
       <c r="T9" s="161" t="n">
         <v>60559.18353623334</v>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="P10" s="162" t="n">
-        <v>73397.09989197367</v>
+        <v>73397.09989197369</v>
       </c>
       <c r="Q10" s="163" t="n">
         <v>0</v>
@@ -2224,7 +2224,7 @@
         <v>157.1576414906223</v>
       </c>
       <c r="T10" s="161" t="n">
-        <v>73726.63092469225</v>
+        <v>73726.63092469226</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" thickBot="1">
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="P12" s="165" t="n">
-        <v>190668.9704254212</v>
+        <v>190668.9704254213</v>
       </c>
       <c r="Q12" s="166" t="n">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>833.2598252199089</v>
       </c>
       <c r="T12" s="168" t="n">
-        <v>192337.2504585911</v>
+        <v>192337.2504585912</v>
       </c>
     </row>
     <row r="13"/>
@@ -2597,7 +2597,7 @@
         <v>101.1285692865419</v>
       </c>
       <c r="U25" s="179" t="n">
-        <v>0.362398812367716</v>
+        <v>0.3623988123677161</v>
       </c>
       <c r="W25" s="175" t="n">
         <v>1</v>
@@ -2669,13 +2669,13 @@
         <v>1182.582051775061</v>
       </c>
       <c r="S26" s="187" t="n">
-        <v>79339.75577026584</v>
+        <v>79339.75577026587</v>
       </c>
       <c r="T26" s="84" t="n">
         <v>34.07302870312817</v>
       </c>
       <c r="U26" s="188" t="n">
-        <v>0.1221022429457826</v>
+        <v>0.1221022429457827</v>
       </c>
       <c r="W26" s="184" t="n">
         <v>2</v>
@@ -2741,7 +2741,7 @@
         <v>12710.61385986785</v>
       </c>
       <c r="Q27" s="186" t="n">
-        <v>0.0660850346438968</v>
+        <v>0.06608503464389678</v>
       </c>
       <c r="R27" s="185" t="n">
         <v>895.1741050713456</v>
@@ -2897,7 +2897,7 @@
         <v>9212.535368124589</v>
       </c>
       <c r="Q29" s="186" t="n">
-        <v>0.04789782190480042</v>
+        <v>0.0478978219048004</v>
       </c>
       <c r="R29" s="185" t="n">
         <v>1193.081652027774</v>
@@ -2975,7 +2975,7 @@
         <v>8622.353500927462</v>
       </c>
       <c r="Q30" s="186" t="n">
-        <v>0.0448293478271584</v>
+        <v>0.04482934782715839</v>
       </c>
       <c r="R30" s="185" t="n">
         <v>1192.30014280217</v>
@@ -2987,7 +2987,7 @@
         <v>7.231697113331732</v>
       </c>
       <c r="U30" s="197" t="n">
-        <v>0.02591511443070746</v>
+        <v>0.02591511443070747</v>
       </c>
       <c r="W30" s="184" t="n">
         <v>6</v>
@@ -3039,7 +3039,7 @@
         <v>7414.644453058579</v>
       </c>
       <c r="Q31" s="186" t="n">
-        <v>0.03855022589425495</v>
+        <v>0.03855022589425494</v>
       </c>
       <c r="R31" s="185" t="n">
         <v>322.7872370894611</v>
@@ -3051,7 +3051,7 @@
         <v>22.97068657334675</v>
       </c>
       <c r="U31" s="197" t="n">
-        <v>0.0823164966357309</v>
+        <v>0.08231649663573093</v>
       </c>
       <c r="W31" s="184" t="n">
         <v>7</v>
@@ -3111,7 +3111,7 @@
         <v>5520.587381943594</v>
       </c>
       <c r="Q32" s="186" t="n">
-        <v>0.02870264272147396</v>
+        <v>0.02870264272147395</v>
       </c>
       <c r="R32" s="185" t="n">
         <v>605.7455480868618</v>
@@ -3123,7 +3123,7 @@
         <v>9.113706901155732</v>
       </c>
       <c r="U32" s="197" t="n">
-        <v>0.03265938182006723</v>
+        <v>0.03265938182006724</v>
       </c>
       <c r="W32" s="184" t="n">
         <v>8</v>
@@ -3189,7 +3189,7 @@
         <v>5512.525795291357</v>
       </c>
       <c r="Q33" s="186" t="n">
-        <v>0.02866072891313462</v>
+        <v>0.02866072891313461</v>
       </c>
       <c r="R33" s="185" t="n">
         <v>1249.337230175964</v>
@@ -3267,7 +3267,7 @@
         <v>4246.04801853447</v>
       </c>
       <c r="Q34" s="186" t="n">
-        <v>0.02207605655384273</v>
+        <v>0.02207605655384272</v>
       </c>
       <c r="R34" s="185" t="n">
         <v>962.3076730454776</v>
@@ -3501,7 +3501,7 @@
         <v>3096.357251540813</v>
       </c>
       <c r="Q37" s="186" t="n">
-        <v>0.01609858331736648</v>
+        <v>0.01609858331736647</v>
       </c>
       <c r="R37" s="185" t="n">
         <v>687.083825251457</v>
@@ -3649,7 +3649,7 @@
         <v>0</v>
       </c>
       <c r="S39" s="187" t="n">
-        <v>3888.543900562525</v>
+        <v>3888.543900562526</v>
       </c>
       <c r="T39" s="84" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0.01341634195306942</v>
       </c>
       <c r="R41" s="185" t="n">
-        <v>376.4008907706191</v>
+        <v>376.400890770619</v>
       </c>
       <c r="S41" s="187" t="n">
-        <v>3821.911274583055</v>
+        <v>3821.911274583056</v>
       </c>
       <c r="T41" s="84" t="n">
         <v>6.855622252068915</v>
       </c>
       <c r="U41" s="197" t="n">
-        <v>0.02456743311726148</v>
+        <v>0.0245674331172615</v>
       </c>
       <c r="W41" s="184" t="n">
         <v>17</v>
@@ -3955,7 +3955,7 @@
         <v>1918.235475831963</v>
       </c>
       <c r="Q43" s="186" t="n">
-        <v>0.009973291555631061</v>
+        <v>0.009973291555631059</v>
       </c>
       <c r="R43" s="185" t="n">
         <v>0</v>
@@ -4035,7 +4035,7 @@
         <v>1595.870947226147</v>
       </c>
       <c r="Q44" s="207" t="n">
-        <v>0.008297253617908651</v>
+        <v>0.008297253617908649</v>
       </c>
       <c r="R44" s="206" t="n">
         <v>1499.790636967547</v>
@@ -4047,7 +4047,7 @@
         <v>1.064062481716026</v>
       </c>
       <c r="U44" s="209" t="n">
-        <v>0.003813116138984571</v>
+        <v>0.003813116138984573</v>
       </c>
       <c r="W44" s="205" t="n">
         <v>20</v>
@@ -4255,7 +4255,7 @@
         <v>17437.41182150781</v>
       </c>
       <c r="Q49" s="177" t="n">
-        <v>0.3654274130465961</v>
+        <v>0.365427413046596</v>
       </c>
       <c r="R49" s="176" t="n">
         <v>292.2510967889699</v>
@@ -4404,7 +4404,7 @@
         <v>3146.661061732651</v>
       </c>
       <c r="Q51" s="186" t="n">
-        <v>0.06594305527068689</v>
+        <v>0.06594305527068688</v>
       </c>
       <c r="R51" s="185" t="n">
         <v>462.0261522616343</v>
@@ -4479,7 +4479,7 @@
         <v>2626.688277476736</v>
       </c>
       <c r="Q52" s="186" t="n">
-        <v>0.05504623690393201</v>
+        <v>0.05504623690393199</v>
       </c>
       <c r="R52" s="185" t="n">
         <v>340.1727607252482</v>
@@ -4554,7 +4554,7 @@
         <v>2618.994149261279</v>
       </c>
       <c r="Q53" s="186" t="n">
-        <v>0.05488499477704966</v>
+        <v>0.05488499477704965</v>
       </c>
       <c r="R53" s="185" t="n">
         <v>318.2049728473172</v>
@@ -4629,7 +4629,7 @@
         <v>2204.171442905709</v>
       </c>
       <c r="Q54" s="186" t="n">
-        <v>0.04619175577987629</v>
+        <v>0.04619175577987628</v>
       </c>
       <c r="R54" s="185" t="n">
         <v>362.7785269174379</v>
@@ -4704,7 +4704,7 @@
         <v>1816.384240255893</v>
       </c>
       <c r="Q55" s="186" t="n">
-        <v>0.03806508676916268</v>
+        <v>0.03806508676916267</v>
       </c>
       <c r="R55" s="185" t="n">
         <v>274.4388011263272</v>
@@ -4779,7 +4779,7 @@
         <v>1617.184514099944</v>
       </c>
       <c r="Q56" s="186" t="n">
-        <v>0.03389055436986627</v>
+        <v>0.03389055436986626</v>
       </c>
       <c r="R56" s="185" t="n">
         <v>410.9533004033252</v>
@@ -5001,10 +5001,10 @@
         </is>
       </c>
       <c r="P59" s="185" t="n">
-        <v>952.0697038192393</v>
+        <v>952.0697038192394</v>
       </c>
       <c r="Q59" s="186" t="n">
-        <v>0.01995206470249091</v>
+        <v>0.0199520647024909</v>
       </c>
       <c r="R59" s="185" t="n">
         <v>379.9595788246066</v>
@@ -5379,7 +5379,7 @@
         <v>545.1650508996471</v>
       </c>
       <c r="Q64" s="186" t="n">
-        <v>0.01142476052483617</v>
+        <v>0.01142476052483616</v>
       </c>
       <c r="R64" s="185" t="n">
         <v>300.1666183418693</v>
@@ -5454,7 +5454,7 @@
         <v>417.0344534799498</v>
       </c>
       <c r="Q65" s="186" t="n">
-        <v>0.008739589512849016</v>
+        <v>0.008739589512849014</v>
       </c>
       <c r="R65" s="185" t="n">
         <v>202.8809073388443</v>
@@ -5530,7 +5530,7 @@
         <v>316.9856436651576</v>
       </c>
       <c r="Q66" s="186" t="n">
-        <v>0.006642914953387414</v>
+        <v>0.006642914953387413</v>
       </c>
       <c r="R66" s="185" t="n">
         <v>287.3615331835319</v>
@@ -5602,13 +5602,13 @@
         </is>
       </c>
       <c r="P67" s="185" t="n">
-        <v>309.6618823922784</v>
+        <v>309.6618823922785</v>
       </c>
       <c r="Q67" s="186" t="n">
         <v>0.006489434427543661</v>
       </c>
       <c r="R67" s="185" t="n">
-        <v>274.8567473378955</v>
+        <v>274.8567473378956</v>
       </c>
       <c r="S67" s="187" t="n">
         <v>639.888431499952</v>
@@ -5680,7 +5680,7 @@
         <v>234.6094239058071</v>
       </c>
       <c r="Q68" s="207" t="n">
-        <v>0.004916596323572866</v>
+        <v>0.004916596323572865</v>
       </c>
       <c r="R68" s="206" t="n">
         <v>239.5502416786515</v>
@@ -5885,7 +5885,7 @@
         <v>21614.54730632594</v>
       </c>
       <c r="Q73" s="177" t="n">
-        <v>0.3569160950360846</v>
+        <v>0.3569160950360845</v>
       </c>
       <c r="R73" s="176" t="n">
         <v>890.5556007736709</v>
@@ -6110,7 +6110,7 @@
         <v>5512.525795291357</v>
       </c>
       <c r="Q76" s="186" t="n">
-        <v>0.09102708249019147</v>
+        <v>0.09102708249019145</v>
       </c>
       <c r="R76" s="185" t="n">
         <v>1249.337230175964</v>
@@ -6185,7 +6185,7 @@
         <v>4448.781423880319</v>
       </c>
       <c r="Q77" s="186" t="n">
-        <v>0.07346171404735925</v>
+        <v>0.07346171404735924</v>
       </c>
       <c r="R77" s="185" t="n">
         <v>435.7622560287422</v>
@@ -6260,7 +6260,7 @@
         <v>3316.415939037885</v>
       </c>
       <c r="Q78" s="186" t="n">
-        <v>0.05476322079298892</v>
+        <v>0.05476322079298891</v>
       </c>
       <c r="R78" s="185" t="n">
         <v>1091.67959042571</v>
@@ -6335,7 +6335,7 @@
         <v>2786.695369148534</v>
       </c>
       <c r="Q79" s="186" t="n">
-        <v>0.04601606571332354</v>
+        <v>0.04601606571332353</v>
       </c>
       <c r="R79" s="185" t="n">
         <v>824.4928512226442</v>
@@ -7385,7 +7385,7 @@
         <v>26170.09160450426</v>
       </c>
       <c r="Q97" s="177" t="n">
-        <v>0.3549611758502242</v>
+        <v>0.3549611758502241</v>
       </c>
       <c r="R97" s="176" t="n">
         <v>1528.424814928359</v>
@@ -7610,7 +7610,7 @@
         <v>7188.889726137993</v>
       </c>
       <c r="Q100" s="186" t="n">
-        <v>0.09750736790727701</v>
+        <v>0.09750736790727696</v>
       </c>
       <c r="R100" s="185" t="n">
         <v>1141.007090136034</v>
@@ -7760,7 +7760,7 @@
         <v>3184.536013900853</v>
       </c>
       <c r="Q102" s="186" t="n">
-        <v>0.04319383612081344</v>
+        <v>0.04319383612081343</v>
       </c>
       <c r="R102" s="185" t="n">
         <v>962.3076730454776</v>
@@ -7836,7 +7836,7 @@
         <v>2679.807060116694</v>
       </c>
       <c r="Q103" s="186" t="n">
-        <v>0.0363478844280023</v>
+        <v>0.03634788442800229</v>
       </c>
       <c r="R103" s="185" t="n">
         <v>843.652101957246</v>
@@ -8286,7 +8286,7 @@
         <v>914.0056870913653</v>
       </c>
       <c r="Q109" s="186" t="n">
-        <v>0.01239722574635172</v>
+        <v>0.01239722574635171</v>
       </c>
       <c r="R109" s="185" t="n">
         <v>185.3318426730689</v>
@@ -8361,7 +8361,7 @@
         <v>804.2544769804459</v>
       </c>
       <c r="Q110" s="186" t="n">
-        <v>0.01090860204641588</v>
+        <v>0.01090860204641587</v>
       </c>
       <c r="R110" s="185" t="n">
         <v>0</v>
@@ -8416,7 +8416,7 @@
         <v>539.0240120297055</v>
       </c>
       <c r="Q111" s="186" t="n">
-        <v>0.007311116828060261</v>
+        <v>0.00731111682806026</v>
       </c>
       <c r="R111" s="185" t="n">
         <v>547.8996238435642</v>
@@ -8491,7 +8491,7 @@
         <v>498.1725488015753</v>
       </c>
       <c r="Q112" s="186" t="n">
-        <v>0.006757023107571964</v>
+        <v>0.006757023107571963</v>
       </c>
       <c r="R112" s="185" t="n">
         <v>137.146327591756</v>
@@ -8621,7 +8621,7 @@
         <v>62.49314842044184</v>
       </c>
       <c r="Q114" s="186" t="n">
-        <v>0.0008476333129107065</v>
+        <v>0.0008476333129107063</v>
       </c>
       <c r="R114" s="185" t="n">
         <v>1342.178813679337</v>
@@ -9596,7 +9596,7 @@
         <v>4.506520365848544</v>
       </c>
       <c r="R154" s="240" t="n">
-        <v>6398.884314999521</v>
+        <v>6398.88431499952</v>
       </c>
       <c r="T154" s="172" t="n"/>
       <c r="U154" s="172" t="n"/>
@@ -9683,7 +9683,7 @@
         </is>
       </c>
       <c r="O158" s="239" t="n">
-        <v>1561.471198555859</v>
+        <v>1561.47119855586</v>
       </c>
       <c r="P158" s="84" t="n">
         <v>7.487248693337843</v>
@@ -10632,7 +10632,7 @@
         <v>0</v>
       </c>
       <c r="R208" s="240" t="n">
-        <v>2571.83128823424</v>
+        <v>2571.831288234241</v>
       </c>
       <c r="T208" s="172" t="n"/>
       <c r="U208" s="172" t="n"/>
@@ -12014,7 +12014,7 @@
         <v>4.506520365848544</v>
       </c>
       <c r="R307" s="240" t="n">
-        <v>6398.884314999521</v>
+        <v>6398.88431499952</v>
       </c>
     </row>
     <row r="308">
@@ -12093,7 +12093,7 @@
         </is>
       </c>
       <c r="O311" s="239" t="n">
-        <v>1561.471198555859</v>
+        <v>1561.47119855586</v>
       </c>
       <c r="P311" s="84" t="n">
         <v>7.487248693337843</v>
@@ -12814,7 +12814,7 @@
         <v>0</v>
       </c>
       <c r="R354" s="240" t="n">
-        <v>2571.83128823424</v>
+        <v>2571.831288234241</v>
       </c>
     </row>
     <row r="355">
@@ -16382,7 +16382,7 @@
         <v>0.1280788980946517</v>
       </c>
       <c r="AN648" s="189" t="n">
-        <v>0.0004589765373556459</v>
+        <v>0.000458976537355646</v>
       </c>
       <c r="AO648" s="190" t="n">
         <v>854.4641302888612</v>
@@ -16502,7 +16502,7 @@
         <v>0.9981113886434008</v>
       </c>
       <c r="AN653" s="189" t="n">
-        <v>0.003576777407284027</v>
+        <v>0.003576777407284028</v>
       </c>
       <c r="AO653" s="190" t="n">
         <v>511.6942797803975</v>
@@ -16790,7 +16790,7 @@
         <v>0.2111449839705193</v>
       </c>
       <c r="AN665" s="189" t="n">
-        <v>0.0007566476216182334</v>
+        <v>0.0007566476216182336</v>
       </c>
       <c r="AO665" s="190" t="n">
         <v>62.59346131323852</v>
@@ -16814,7 +16814,7 @@
         <v>0.0714425083209866</v>
       </c>
       <c r="AN666" s="189" t="n">
-        <v>0.0002560174671782065</v>
+        <v>0.0002560174671782066</v>
       </c>
       <c r="AO666" s="190" t="n">
         <v>48.08879897687814</v>
@@ -16862,7 +16862,7 @@
         <v>1.21370812127122</v>
       </c>
       <c r="AN668" s="189" t="n">
-        <v>0.004349378072021005</v>
+        <v>0.004349378072021006</v>
       </c>
       <c r="AO668" s="190" t="n">
         <v>32.82837726414397</v>
@@ -16886,7 +16886,7 @@
         <v>0.05278624599262982</v>
       </c>
       <c r="AN669" s="189" t="n">
-        <v>0.0001891619054045583</v>
+        <v>0.0001891619054045584</v>
       </c>
       <c r="AO669" s="190" t="n">
         <v>18.93642064210956</v>
@@ -17290,10 +17290,10 @@
         <v>0</v>
       </c>
       <c r="R8" s="159" t="n">
-        <v>2.628116440802515</v>
+        <v>2.628116440802514</v>
       </c>
       <c r="S8" s="160" t="n">
-        <v>69.06548989563152</v>
+        <v>69.06548989563149</v>
       </c>
       <c r="T8" s="161" t="n">
         <v>37278.72423869542</v>
@@ -17312,10 +17312,10 @@
         <v>0</v>
       </c>
       <c r="R9" s="163" t="n">
-        <v>23.72042364117519</v>
+        <v>23.7204236411752</v>
       </c>
       <c r="S9" s="164" t="n">
-        <v>67.7992674494067</v>
+        <v>67.79926744940671</v>
       </c>
       <c r="T9" s="161" t="n">
         <v>42805.93416793523</v>
@@ -17776,10 +17776,10 @@
         </is>
       </c>
       <c r="P26" s="185" t="n">
-        <v>26522.14923286874</v>
+        <v>26522.14923286875</v>
       </c>
       <c r="Q26" s="186" t="n">
-        <v>0.160896122444812</v>
+        <v>0.1608961224448121</v>
       </c>
       <c r="R26" s="185" t="n">
         <v>417.5496689725574</v>
@@ -18022,10 +18022,10 @@
         <v>17044.66297125358</v>
       </c>
       <c r="T29" s="84" t="n">
-        <v>6.942429228798463</v>
+        <v>6.942429228798462</v>
       </c>
       <c r="U29" s="188" t="n">
-        <v>0.03077366959282203</v>
+        <v>0.03077366959282202</v>
       </c>
       <c r="W29" s="184" t="n">
         <v>5</v>
@@ -18224,13 +18224,13 @@
         </is>
       </c>
       <c r="P32" s="185" t="n">
-        <v>5758.614189381809</v>
+        <v>5758.61418938181</v>
       </c>
       <c r="Q32" s="186" t="n">
-        <v>0.03493452531286392</v>
+        <v>0.03493452531286393</v>
       </c>
       <c r="R32" s="185" t="n">
-        <v>629.9102787609263</v>
+        <v>629.9102787609264</v>
       </c>
       <c r="S32" s="187" t="n">
         <v>8154.317491039048</v>
@@ -18762,13 +18762,13 @@
         <v>0.01649363280264182</v>
       </c>
       <c r="R39" s="185" t="n">
-        <v>400.5389410385686</v>
+        <v>400.5389410385685</v>
       </c>
       <c r="S39" s="187" t="n">
         <v>3957.12810800627</v>
       </c>
       <c r="T39" s="84" t="n">
-        <v>6.787888704218473</v>
+        <v>6.787888704218474</v>
       </c>
       <c r="U39" s="197" t="n">
         <v>0.03008863862089679</v>
@@ -22393,7 +22393,7 @@
         <v>33401.23966684753</v>
       </c>
       <c r="Q97" s="177" t="n">
-        <v>0.4526293208813876</v>
+        <v>0.4526293208813877</v>
       </c>
       <c r="R97" s="176" t="n">
         <v>1551.914559664297</v>
@@ -22546,13 +22546,13 @@
         <v>0.09669186212830948</v>
       </c>
       <c r="R99" s="185" t="n">
-        <v>1179.682438715551</v>
+        <v>1179.68243871555</v>
       </c>
       <c r="S99" s="187" t="n">
         <v>14210.99268388258</v>
       </c>
       <c r="T99" s="84" t="n">
-        <v>6.048458591321878</v>
+        <v>6.048458591321879</v>
       </c>
       <c r="U99" s="197" t="n">
         <v>0.07881238982929574</v>
@@ -24477,7 +24477,7 @@
         </is>
       </c>
       <c r="O150" s="239" t="n">
-        <v>5758.614189381809</v>
+        <v>5758.61418938181</v>
       </c>
       <c r="P150" s="84" t="n">
         <v>9.141959392549317</v>
@@ -24558,7 +24558,7 @@
         <v>4.775784957707994</v>
       </c>
       <c r="R153" s="240" t="n">
-        <v>6781.217652820743</v>
+        <v>6781.217652820742</v>
       </c>
       <c r="T153" s="172" t="n"/>
       <c r="U153" s="172" t="n"/>
@@ -24750,7 +24750,7 @@
         <v>2.227141504817263</v>
       </c>
       <c r="R161" s="240" t="n">
-        <v>9700.002168606863</v>
+        <v>9700.002168606865</v>
       </c>
       <c r="T161" s="172" t="n"/>
       <c r="U161" s="172" t="n"/>
@@ -25618,7 +25618,7 @@
         <v>0</v>
       </c>
       <c r="R208" s="240" t="n">
-        <v>2648.90429592809</v>
+        <v>2648.904295928089</v>
       </c>
       <c r="T208" s="172" t="n"/>
       <c r="U208" s="172" t="n"/>
@@ -26903,7 +26903,7 @@
         </is>
       </c>
       <c r="O303" s="239" t="n">
-        <v>5758.614189381809</v>
+        <v>5758.61418938181</v>
       </c>
       <c r="P303" s="84" t="n">
         <v>9.141959392549317</v>
@@ -26978,7 +26978,7 @@
         <v>4.775784957707994</v>
       </c>
       <c r="R306" s="240" t="n">
-        <v>6781.217652820743</v>
+        <v>6781.217652820742</v>
       </c>
     </row>
     <row r="307">
@@ -27800,7 +27800,7 @@
         <v>0</v>
       </c>
       <c r="R354" s="240" t="n">
-        <v>2648.90429592809</v>
+        <v>2648.904295928089</v>
       </c>
     </row>
     <row r="355">
@@ -28926,7 +28926,7 @@
         <v>2.227141504817263</v>
       </c>
       <c r="R454" s="240" t="n">
-        <v>9700.002168606863</v>
+        <v>9700.002168606865</v>
       </c>
     </row>
     <row r="455">
@@ -31275,7 +31275,7 @@
         <v>0.005921696522424239</v>
       </c>
       <c r="AO644" s="190" t="n">
-        <v>1120.160331729499</v>
+        <v>1120.160331729498</v>
       </c>
     </row>
     <row r="645">
@@ -32351,7 +32351,7 @@
         <v>0</v>
       </c>
       <c r="S8" s="160" t="n">
-        <v>31.64877607297112</v>
+        <v>31.64877607297113</v>
       </c>
       <c r="T8" s="161" t="n">
         <v>28608.67937477024</v>
@@ -32364,7 +32364,7 @@
         </is>
       </c>
       <c r="P9" s="162" t="n">
-        <v>34601.56295167859</v>
+        <v>34601.56295167858</v>
       </c>
       <c r="Q9" s="163" t="n">
         <v>0</v>
@@ -32373,7 +32373,7 @@
         <v>0</v>
       </c>
       <c r="S9" s="164" t="n">
-        <v>76.89562758077339</v>
+        <v>76.89562758077342</v>
       </c>
       <c r="T9" s="161" t="n">
         <v>34678.45857925936</v>
@@ -32386,7 +32386,7 @@
         </is>
       </c>
       <c r="P10" s="162" t="n">
-        <v>78396.68197083156</v>
+        <v>78396.68197083157</v>
       </c>
       <c r="Q10" s="163" t="n">
         <v>0</v>
@@ -32398,7 +32398,7 @@
         <v>106.478587110114</v>
       </c>
       <c r="T10" s="161" t="n">
-        <v>78503.16055794168</v>
+        <v>78503.16055794169</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" thickBot="1">
@@ -32439,7 +32439,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="167" t="n">
-        <v>441.1306784941807</v>
+        <v>441.1306784941808</v>
       </c>
       <c r="T12" s="168" t="n">
         <v>153737.5521696368</v>
@@ -32990,19 +32990,19 @@
         </is>
       </c>
       <c r="P28" s="185" t="n">
-        <v>9745.4290075194</v>
+        <v>9745.429007519399</v>
       </c>
       <c r="Q28" s="186" t="n">
-        <v>0.06339003626626055</v>
+        <v>0.06339003626626054</v>
       </c>
       <c r="R28" s="185" t="n">
-        <v>334.3487604398621</v>
+        <v>334.348760439862</v>
       </c>
       <c r="S28" s="187" t="n">
         <v>40769.78412054475</v>
       </c>
       <c r="T28" s="84" t="n">
-        <v>29.1474955513474</v>
+        <v>29.14749555134741</v>
       </c>
       <c r="U28" s="188" t="n">
         <v>0.170082818609734</v>
@@ -33313,10 +33313,10 @@
         </is>
       </c>
       <c r="Z32" s="84" t="n">
-        <v>9.393915268543525</v>
+        <v>9.393915268543527</v>
       </c>
       <c r="AA32" s="189" t="n">
-        <v>0.05481581029286889</v>
+        <v>0.0548158102928689</v>
       </c>
       <c r="AB32" s="190" t="n">
         <v>9991.719500892608</v>
@@ -33631,7 +33631,7 @@
         <v>0</v>
       </c>
       <c r="AB36" s="190" t="n">
-        <v>7860.324361552336</v>
+        <v>7860.324361552335</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickBot="1">
@@ -35995,7 +35995,7 @@
         <v>11180.91914627704</v>
       </c>
       <c r="Q73" s="177" t="n">
-        <v>0.3224168433185253</v>
+        <v>0.3224168433185255</v>
       </c>
       <c r="R73" s="176" t="n">
         <v>1745.003832795251</v>
@@ -36070,7 +36070,7 @@
         <v>6602.046907443629</v>
       </c>
       <c r="Q74" s="186" t="n">
-        <v>0.1903789031555228</v>
+        <v>0.1903789031555229</v>
       </c>
       <c r="R74" s="185" t="n">
         <v>1367.344207795734</v>
@@ -36295,7 +36295,7 @@
         <v>1574.431586793387</v>
       </c>
       <c r="Q77" s="186" t="n">
-        <v>0.04540085261272339</v>
+        <v>0.0454008526127234</v>
       </c>
       <c r="R77" s="185" t="n">
         <v>819.9158697615667</v>
@@ -36445,7 +36445,7 @@
         <v>1536.379945536515</v>
       </c>
       <c r="Q79" s="186" t="n">
-        <v>0.04430358235286154</v>
+        <v>0.04430358235286155</v>
       </c>
       <c r="R79" s="185" t="n">
         <v>650.5954683531687</v>
@@ -36520,7 +36520,7 @@
         <v>1441.812754014633</v>
       </c>
       <c r="Q80" s="186" t="n">
-        <v>0.04157661018061968</v>
+        <v>0.04157661018061969</v>
       </c>
       <c r="R80" s="185" t="n">
         <v>1680.019703635118</v>
@@ -36595,7 +36595,7 @@
         <v>1285.215825748591</v>
       </c>
       <c r="Q81" s="186" t="n">
-        <v>0.03706092711160059</v>
+        <v>0.0370609271116006</v>
       </c>
       <c r="R81" s="185" t="n">
         <v>1064.71973903936</v>
@@ -37407,13 +37407,13 @@
         <v>41526.77769111138</v>
       </c>
       <c r="Q97" s="177" t="n">
-        <v>0.5289822396444951</v>
+        <v>0.528982239644495</v>
       </c>
       <c r="R97" s="176" t="n">
         <v>1610.338386144384</v>
       </c>
       <c r="S97" s="178" t="n">
-        <v>79149.76354203306</v>
+        <v>79149.76354203305</v>
       </c>
       <c r="T97" s="72" t="n">
         <v>25.78760964056661</v>
@@ -37554,13 +37554,13 @@
         </is>
       </c>
       <c r="P99" s="185" t="n">
-        <v>7230.760258223349</v>
+        <v>7230.760258223348</v>
       </c>
       <c r="Q99" s="186" t="n">
-        <v>0.09210788720903107</v>
+        <v>0.09210788720903103</v>
       </c>
       <c r="R99" s="185" t="n">
-        <v>1245.282880245893</v>
+        <v>1245.282880245892</v>
       </c>
       <c r="S99" s="187" t="n">
         <v>13992.14339655079</v>
@@ -37632,7 +37632,7 @@
         <v>3855.647477245774</v>
       </c>
       <c r="Q100" s="186" t="n">
-        <v>0.04911455092817562</v>
+        <v>0.04911455092817561</v>
       </c>
       <c r="R100" s="185" t="n">
         <v>1064.71973903936</v>
@@ -37707,7 +37707,7 @@
         <v>3120.721621618522</v>
       </c>
       <c r="Q101" s="186" t="n">
-        <v>0.03975281503876748</v>
+        <v>0.03975281503876747</v>
       </c>
       <c r="R101" s="185" t="n">
         <v>935.0466305843712</v>
@@ -37782,7 +37782,7 @@
         <v>2991.490566416176</v>
       </c>
       <c r="Q102" s="186" t="n">
-        <v>0.0381066258371625</v>
+        <v>0.03810662583716249</v>
       </c>
       <c r="R102" s="185" t="n">
         <v>778.8888989206384</v>
@@ -37858,7 +37858,7 @@
         <v>2991.490566416176</v>
       </c>
       <c r="Q103" s="186" t="n">
-        <v>0.0381066258371625</v>
+        <v>0.03810662583716249</v>
       </c>
       <c r="R103" s="185" t="n">
         <v>778.8888989206384</v>
@@ -37886,10 +37886,10 @@
         </is>
       </c>
       <c r="Z103" s="84" t="n">
-        <v>1.596965595652399</v>
+        <v>1.5969655956524</v>
       </c>
       <c r="AA103" s="189" t="n">
-        <v>0.02186865021814413</v>
+        <v>0.02186865021814414</v>
       </c>
       <c r="AB103" s="190" t="n">
         <v>2562.952940567171</v>
@@ -38233,7 +38233,7 @@
         <v>561.3561067398261</v>
       </c>
       <c r="Q108" s="186" t="n">
-        <v>0.007150745304394464</v>
+        <v>0.007150745304394463</v>
       </c>
       <c r="R108" s="185" t="n">
         <v>0</v>
@@ -38308,7 +38308,7 @@
         <v>477.9959493529775</v>
       </c>
       <c r="Q109" s="186" t="n">
-        <v>0.006088875224331609</v>
+        <v>0.006088875224331608</v>
       </c>
       <c r="R109" s="185" t="n">
         <v>144.4212983457928</v>
@@ -38383,7 +38383,7 @@
         <v>390.2886008527829</v>
       </c>
       <c r="Q110" s="186" t="n">
-        <v>0.004971629143067665</v>
+        <v>0.004971629143067664</v>
       </c>
       <c r="R110" s="185" t="n">
         <v>323.3293342057707</v>
@@ -38438,7 +38438,7 @@
         <v>156.1799942569007</v>
       </c>
       <c r="Q111" s="186" t="n">
-        <v>0.001989473966995599</v>
+        <v>0.001989473966995598</v>
       </c>
       <c r="R111" s="185" t="n">
         <v>400.8831889701711</v>
@@ -38513,7 +38513,7 @@
         <v>63.47729586781411</v>
       </c>
       <c r="Q112" s="186" t="n">
-        <v>0.0008085954172630125</v>
+        <v>0.0008085954172630124</v>
       </c>
       <c r="R112" s="185" t="n">
         <v>1479.292057785772</v>
@@ -39421,7 +39421,7 @@
         </is>
       </c>
       <c r="O148" s="239" t="n">
-        <v>9745.4290075194</v>
+        <v>9745.429007519399</v>
       </c>
       <c r="P148" s="84" t="n">
         <v>29.1474955513474</v>
@@ -40166,7 +40166,7 @@
         <v>0</v>
       </c>
       <c r="R183" s="240" t="n">
-        <v>7860.324361552336</v>
+        <v>7860.324361552335</v>
       </c>
       <c r="T183" s="172" t="n"/>
       <c r="U183" s="172" t="n"/>
@@ -40767,7 +40767,7 @@
         <v>0</v>
       </c>
       <c r="R214" s="240" t="n">
-        <v>3919.557779635086</v>
+        <v>3919.557779635085</v>
       </c>
       <c r="T214" s="172" t="n"/>
       <c r="U214" s="172" t="n"/>
@@ -41851,7 +41851,7 @@
         </is>
       </c>
       <c r="O301" s="239" t="n">
-        <v>9745.4290075194</v>
+        <v>9745.429007519399</v>
       </c>
       <c r="P301" s="84" t="n">
         <v>29.1474955513474</v>
@@ -42420,7 +42420,7 @@
         <v>0</v>
       </c>
       <c r="R330" s="240" t="n">
-        <v>7860.324361552336</v>
+        <v>7860.324361552335</v>
       </c>
     </row>
     <row r="331">
@@ -44024,7 +44024,7 @@
         <v>0</v>
       </c>
       <c r="R460" s="240" t="n">
-        <v>3919.557779635086</v>
+        <v>3919.557779635085</v>
       </c>
     </row>
     <row r="461">
@@ -45541,10 +45541,10 @@
         </is>
       </c>
       <c r="AM614" s="84" t="n">
-        <v>9.393915268543525</v>
+        <v>9.393915268543527</v>
       </c>
       <c r="AN614" s="189" t="n">
-        <v>0.05481581029286889</v>
+        <v>0.0548158102928689</v>
       </c>
       <c r="AO614" s="190" t="n">
         <v>9991.719500892608</v>
@@ -45643,7 +45643,7 @@
         <v>0</v>
       </c>
       <c r="AO618" s="190" t="n">
-        <v>7860.324361552336</v>
+        <v>7860.324361552335</v>
       </c>
     </row>
     <row r="619">
@@ -47374,7 +47374,7 @@
         </is>
       </c>
       <c r="P9" s="162" t="n">
-        <v>37504.02978221951</v>
+        <v>37504.0297822195</v>
       </c>
       <c r="Q9" s="163" t="n">
         <v>0</v>
@@ -47383,10 +47383,10 @@
         <v>0</v>
       </c>
       <c r="S9" s="164" t="n">
-        <v>85.04813915965248</v>
+        <v>85.04813915965249</v>
       </c>
       <c r="T9" s="161" t="n">
-        <v>37589.07792137916</v>
+        <v>37589.07792137915</v>
       </c>
     </row>
     <row r="10">
@@ -47847,7 +47847,7 @@
         <v>11957.11386915134</v>
       </c>
       <c r="Q26" s="186" t="n">
-        <v>0.07062711982704839</v>
+        <v>0.0706271198270484</v>
       </c>
       <c r="R26" s="185" t="n">
         <v>1352.765962052527</v>
@@ -47925,7 +47925,7 @@
         <v>11542.5411410885</v>
       </c>
       <c r="Q27" s="186" t="n">
-        <v>0.06817836186903801</v>
+        <v>0.06817836186903803</v>
       </c>
       <c r="R27" s="185" t="n">
         <v>10372.95580413289</v>
@@ -48003,7 +48003,7 @@
         <v>11093.33998491467</v>
       </c>
       <c r="Q28" s="186" t="n">
-        <v>0.06552506407236919</v>
+        <v>0.0655250640723692</v>
       </c>
       <c r="R28" s="185" t="n">
         <v>339.2368794120216</v>
@@ -48081,7 +48081,7 @@
         <v>8676.100013225549</v>
       </c>
       <c r="Q29" s="186" t="n">
-        <v>0.05124714558807061</v>
+        <v>0.05124714558807062</v>
       </c>
       <c r="R29" s="185" t="n">
         <v>1356.034136040362</v>
@@ -48220,16 +48220,16 @@
         </is>
       </c>
       <c r="P31" s="185" t="n">
-        <v>6254.517428753081</v>
+        <v>6254.51742875308</v>
       </c>
       <c r="Q31" s="186" t="n">
         <v>0.0369435765800112</v>
       </c>
       <c r="R31" s="185" t="n">
-        <v>686.0358204215186</v>
+        <v>686.0358204215185</v>
       </c>
       <c r="S31" s="187" t="n">
-        <v>8526.973997461853</v>
+        <v>8526.973997461851</v>
       </c>
       <c r="T31" s="84" t="n">
         <v>9.116896294001295</v>
@@ -48407,7 +48407,7 @@
         <v>0</v>
       </c>
       <c r="AB33" s="190" t="n">
-        <v>9633.176503484041</v>
+        <v>9633.176503484043</v>
       </c>
     </row>
     <row r="34">
@@ -48529,7 +48529,7 @@
         <v>4469.377130929079</v>
       </c>
       <c r="Q35" s="186" t="n">
-        <v>0.02639928310733749</v>
+        <v>0.0263992831073375</v>
       </c>
       <c r="R35" s="185" t="n">
         <v>653.2124194089411</v>
@@ -48827,7 +48827,7 @@
         <v>1374.07878237639</v>
       </c>
       <c r="Q39" s="186" t="n">
-        <v>0.008116275204594167</v>
+        <v>0.008116275204594169</v>
       </c>
       <c r="R39" s="185" t="n">
         <v>215.3316853088869</v>
@@ -48899,7 +48899,7 @@
         <v>1217.938663082111</v>
       </c>
       <c r="Q40" s="186" t="n">
-        <v>0.007194001900527244</v>
+        <v>0.007194001900527245</v>
       </c>
       <c r="R40" s="185" t="n">
         <v>520.1835295200572</v>
@@ -48979,7 +48979,7 @@
         <v>1208.641034384585</v>
       </c>
       <c r="Q41" s="186" t="n">
-        <v>0.00713908356962285</v>
+        <v>0.007139083569622851</v>
       </c>
       <c r="R41" s="185" t="n">
         <v>0</v>
@@ -49059,7 +49059,7 @@
         <v>884.4130782099252</v>
       </c>
       <c r="Q42" s="186" t="n">
-        <v>0.005223965342714803</v>
+        <v>0.005223965342714805</v>
       </c>
       <c r="R42" s="185" t="n">
         <v>449.9758725135909</v>
@@ -49219,7 +49219,7 @@
         <v>543.2691942120091</v>
       </c>
       <c r="Q44" s="207" t="n">
-        <v>0.003208929754942518</v>
+        <v>0.003208929754942519</v>
       </c>
       <c r="R44" s="206" t="n">
         <v>344.3641674305946</v>
@@ -50219,7 +50219,7 @@
         <v>1.79239042154759</v>
       </c>
       <c r="AA59" s="189" t="n">
-        <v>0.03100313621382312</v>
+        <v>0.03100313621382311</v>
       </c>
       <c r="AB59" s="190" t="n">
         <v>1076.273739235485</v>
@@ -50895,7 +50895,7 @@
         <v>13774.16338925749</v>
       </c>
       <c r="Q73" s="177" t="n">
-        <v>0.3664405766501471</v>
+        <v>0.3664405766501472</v>
       </c>
       <c r="R73" s="176" t="n">
         <v>1791.442456067793</v>
@@ -51045,7 +51045,7 @@
         <v>6655.996139278031</v>
       </c>
       <c r="Q75" s="186" t="n">
-        <v>0.1770726101129596</v>
+        <v>0.1770726101129597</v>
       </c>
       <c r="R75" s="185" t="n">
         <v>457.9692469679724</v>
@@ -51270,7 +51270,7 @@
         <v>1653.059081336067</v>
       </c>
       <c r="Q78" s="186" t="n">
-        <v>0.04397711177681945</v>
+        <v>0.04397711177681947</v>
       </c>
       <c r="R78" s="185" t="n">
         <v>869.4528610287323</v>
@@ -51420,7 +51420,7 @@
         <v>1407.213034059368</v>
       </c>
       <c r="Q80" s="186" t="n">
-        <v>0.03743675322397311</v>
+        <v>0.03743675322397312</v>
       </c>
       <c r="R80" s="185" t="n">
         <v>1114.43358344224</v>
@@ -51454,7 +51454,7 @@
         <v>0</v>
       </c>
       <c r="AB80" s="190" t="n">
-        <v>4334.929426567819</v>
+        <v>4334.929426567818</v>
       </c>
     </row>
     <row r="81">
@@ -52294,10 +52294,10 @@
         <v>95801.20989777874</v>
       </c>
       <c r="T97" s="72" t="n">
-        <v>30.90719912574198</v>
+        <v>30.90719912574199</v>
       </c>
       <c r="U97" s="213" t="n">
-        <v>0.3763938612713742</v>
+        <v>0.3763938612713743</v>
       </c>
       <c r="W97" s="175" t="n">
         <v>1</v>
@@ -52438,16 +52438,16 @@
         <v>0.07831338400839823</v>
       </c>
       <c r="R99" s="185" t="n">
-        <v>1297.697205715481</v>
+        <v>1297.697205715482</v>
       </c>
       <c r="S99" s="187" t="n">
         <v>13776.66438824391</v>
       </c>
       <c r="T99" s="84" t="n">
-        <v>5.574259437762243</v>
+        <v>5.574259437762242</v>
       </c>
       <c r="U99" s="197" t="n">
-        <v>0.06788441181524763</v>
+        <v>0.06788441181524761</v>
       </c>
       <c r="W99" s="184" t="n">
         <v>3</v>
@@ -52619,7 +52619,7 @@
         <v>0</v>
       </c>
       <c r="AB101" s="190" t="n">
-        <v>4334.929426567818</v>
+        <v>4334.929426567819</v>
       </c>
     </row>
     <row r="102">
@@ -54186,10 +54186,10 @@
         <v>87555.74838878366</v>
       </c>
       <c r="P145" s="72" t="n">
-        <v>68.10200542396777</v>
+        <v>68.10200542396778</v>
       </c>
       <c r="Q145" s="72" t="n">
-        <v>68.10200542396777</v>
+        <v>68.10200542396778</v>
       </c>
       <c r="R145" s="238" t="n">
         <v>164416.923215098</v>
@@ -54312,7 +54312,7 @@
         <v>9.116896294001295</v>
       </c>
       <c r="R150" s="240" t="n">
-        <v>8711.710965408924</v>
+        <v>8711.710965408925</v>
       </c>
       <c r="T150" s="172" t="n"/>
       <c r="U150" s="172" t="n"/>
@@ -54834,7 +54834,7 @@
         <v>0</v>
       </c>
       <c r="R175" s="240" t="n">
-        <v>9633.176503484041</v>
+        <v>9633.176503484043</v>
       </c>
       <c r="T175" s="172" t="n"/>
       <c r="U175" s="172" t="n"/>
@@ -55118,7 +55118,7 @@
         <v>0</v>
       </c>
       <c r="R189" s="240" t="n">
-        <v>4933.735211317693</v>
+        <v>4933.735211317694</v>
       </c>
       <c r="T189" s="172" t="n"/>
       <c r="U189" s="172" t="n"/>
@@ -56644,10 +56644,10 @@
         <v>87555.74838878366</v>
       </c>
       <c r="P299" s="72" t="n">
-        <v>68.10200542396777</v>
+        <v>68.10200542396778</v>
       </c>
       <c r="Q299" s="72" t="n">
-        <v>68.10200542396777</v>
+        <v>68.10200542396778</v>
       </c>
       <c r="R299" s="238" t="n">
         <v>164416.923215098</v>
@@ -56738,7 +56738,7 @@
         <v>9.116896294001295</v>
       </c>
       <c r="R303" s="240" t="n">
-        <v>8711.710965408924</v>
+        <v>8711.710965408925</v>
       </c>
     </row>
     <row r="304">
@@ -57126,7 +57126,7 @@
         <v>0</v>
       </c>
       <c r="R323" s="240" t="n">
-        <v>9633.176503484041</v>
+        <v>9633.176503484043</v>
       </c>
     </row>
     <row r="324">
@@ -57360,7 +57360,7 @@
         <v>0</v>
       </c>
       <c r="R336" s="240" t="n">
-        <v>4933.735211317693</v>
+        <v>4933.735211317694</v>
       </c>
     </row>
     <row r="337">
@@ -60405,7 +60405,7 @@
         <v>0</v>
       </c>
       <c r="AO615" s="190" t="n">
-        <v>9633.176503484041</v>
+        <v>9633.176503484043</v>
       </c>
     </row>
     <row r="616">
@@ -62307,7 +62307,7 @@
         <v>0</v>
       </c>
       <c r="S9" s="164" t="n">
-        <v>93.96726810216605</v>
+        <v>93.96726810216607</v>
       </c>
       <c r="T9" s="161" t="n">
         <v>40844.47533085976</v>
@@ -62373,7 +62373,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="167" t="n">
-        <v>762.7662613941047</v>
+        <v>762.7662613941048</v>
       </c>
       <c r="T12" s="168" t="n">
         <v>180215.2829708577</v>
@@ -62768,10 +62768,10 @@
         </is>
       </c>
       <c r="P26" s="185" t="n">
-        <v>12751.78709975114</v>
+        <v>12751.78709975115</v>
       </c>
       <c r="Q26" s="186" t="n">
-        <v>0.07075863317215562</v>
+        <v>0.07075863317215564</v>
       </c>
       <c r="R26" s="185" t="n">
         <v>347.5791929047166</v>
@@ -62780,7 +62780,7 @@
         <v>51316.19537744212</v>
       </c>
       <c r="T26" s="84" t="n">
-        <v>36.68742939755558</v>
+        <v>36.68742939755559</v>
       </c>
       <c r="U26" s="188" t="n">
         <v>0.1954760080401073</v>
@@ -63381,7 +63381,7 @@
         <v>487.369170286379</v>
       </c>
       <c r="S34" s="187" t="n">
-        <v>4355.625207929461</v>
+        <v>4355.625207929462</v>
       </c>
       <c r="T34" s="84" t="n">
         <v>6.588676923629476</v>
@@ -67143,16 +67143,16 @@
         <v>63263.76262583413</v>
       </c>
       <c r="Q97" s="177" t="n">
-        <v>0.6400986356069732</v>
+        <v>0.6400986356069734</v>
       </c>
       <c r="R97" s="176" t="n">
         <v>1709.953956257046</v>
       </c>
       <c r="S97" s="178" t="n">
-        <v>115799.3123637092</v>
+        <v>115799.3123637093</v>
       </c>
       <c r="T97" s="72" t="n">
-        <v>36.99734860949912</v>
+        <v>36.99734860949913</v>
       </c>
       <c r="U97" s="213" t="n">
         <v>0.4267586540832181</v>
@@ -70046,7 +70046,7 @@
         <v>0</v>
       </c>
       <c r="R195" s="240" t="n">
-        <v>2369.932679494436</v>
+        <v>2369.932679494435</v>
       </c>
       <c r="T195" s="172" t="n"/>
       <c r="U195" s="172" t="n"/>
@@ -72276,7 +72276,7 @@
         <v>0</v>
       </c>
       <c r="R342" s="240" t="n">
-        <v>2369.932679494436</v>
+        <v>2369.932679494435</v>
       </c>
     </row>
     <row r="343">
